--- a/docs/StructureDefinition-BRProblemaDiagnostico.xlsx
+++ b/docs/StructureDefinition-BRProblemaDiagnostico.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -376,7 +376,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -843,7 +843,7 @@
     <t>Coding of the severity with a terminology is preferred, where possible.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-severity</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-severity|4.0.1</t>
   </si>
   <si>
     <t>&lt; 272141005 |Severities|</t>
@@ -958,7 +958,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 442083009  |Anatomical or acquired body structure|</t>
@@ -1196,7 +1196,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1274,7 +1274,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1359,7 +1359,7 @@
     <t>Condition.subject.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1399,7 +1399,7 @@
     <t>Condition.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1499,7 +1499,7 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1588,7 +1588,7 @@
     <t>Codes describing condition stages (e.g. Cancer stages).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-1
@@ -1601,7 +1601,7 @@
     <t>Condition.stage.assessment</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ClinicalImpression|DiagnosticReport|Observation)
+    <t xml:space="preserve">Reference(ClinicalImpression|4.0.1|DiagnosticReport|4.0.1|Observation|4.0.1)
 </t>
   </si>
   <si>
@@ -1626,7 +1626,7 @@
     <t>Codes describing the kind of condition staging (e.g. clinical or pathological).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-stage-type</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-stage-type|4.0.1</t>
   </si>
   <si>
     <t>./inboundRelationship[typeCode=SUBJ].source[classCode=OBS, moodCode=EVN, code="stage type"]</t>
@@ -1672,7 +1672,7 @@
     <t>Codes that describe the manifestation or symptoms of a condition.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom</t>
+    <t>http://hl7.org/fhir/ValueSet/manifestation-or-symptom|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">con-2
@@ -1691,7 +1691,7 @@
     <t>Condition.evidence.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1732,7 +1732,7 @@
     <t>Condition.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -2273,7 +2273,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>157</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>183</v>
       </c>
@@ -5277,7 +5277,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>271</v>
       </c>
@@ -6841,7 +6841,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>304</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>318</v>
       </c>
@@ -7553,7 +7553,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>328</v>
       </c>
@@ -8149,7 +8149,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>345</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>352</v>
       </c>
@@ -13283,7 +13283,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>539</v>
       </c>
@@ -13877,7 +13877,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
         <v>560</v>
       </c>
@@ -13997,12 +13997,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP99">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
